--- a/SOEN 341 Agile planning.xlsx
+++ b/SOEN 341 Agile planning.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet state="visible" name="Cover Page" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Product backlog" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Time blog" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="80">
   <si>
     <t>TEAM NAME</t>
   </si>
@@ -277,6 +278,63 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Sprint 1:</t>
+  </si>
+  <si>
+    <t>Tin</t>
+  </si>
+  <si>
+    <t>Guyass</t>
+  </si>
+  <si>
+    <t>Khaled</t>
+  </si>
+  <si>
+    <t>Jacob</t>
+  </si>
+  <si>
+    <t>Deep</t>
+  </si>
+  <si>
+    <t>Jinyu</t>
+  </si>
+  <si>
+    <t>Login page</t>
+  </si>
+  <si>
+    <t>Registration page</t>
+  </si>
+  <si>
+    <t>Home page</t>
+  </si>
+  <si>
+    <t>Landing page</t>
+  </si>
+  <si>
+    <t>Meal preferences</t>
+  </si>
+  <si>
+    <t>Environment Configuration</t>
+  </si>
+  <si>
+    <t>Database Configuration</t>
+  </si>
+  <si>
+    <t>Sprint Planning</t>
+  </si>
+  <si>
+    <t>User stories</t>
+  </si>
+  <si>
+    <t>Meetings</t>
+  </si>
+  <si>
+    <t>Total (minutes):</t>
+  </si>
+  <si>
+    <t>Total hours</t>
   </si>
 </sst>
 </file>
@@ -351,7 +409,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -414,12 +472,26 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -491,11 +563,102 @@
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1">
+    <tableStyle count="4" pivot="0" name="Time blog-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
@@ -507,8 +670,27 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:G14" displayName="Table1" name="Table1" id="1">
+  <tableColumns count="7">
+    <tableColumn name="Sprint 1:" id="1"/>
+    <tableColumn name="Tin" id="2"/>
+    <tableColumn name="Guyass" id="3"/>
+    <tableColumn name="Khaled" id="4"/>
+    <tableColumn name="Jacob" id="5"/>
+    <tableColumn name="Deep" id="6"/>
+    <tableColumn name="Jinyu" id="7"/>
+  </tableColumns>
+  <tableStyleInfo name="Time blog-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1228,4 +1410,326 @@
   </dataValidations>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="38.88"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="C4" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="D4" s="32">
+        <v>60.0</v>
+      </c>
+      <c r="E4" s="32">
+        <v>60.0</v>
+      </c>
+      <c r="F4" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="G4" s="32">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="C5" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="D5" s="32">
+        <v>60.0</v>
+      </c>
+      <c r="E5" s="32">
+        <v>60.0</v>
+      </c>
+      <c r="F5" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="G5" s="32">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="32">
+        <v>30.0</v>
+      </c>
+      <c r="E6" s="32">
+        <v>30.0</v>
+      </c>
+      <c r="F6" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="G6" s="32">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="C7" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="32">
+        <v>15.0</v>
+      </c>
+      <c r="E7" s="32">
+        <v>15.0</v>
+      </c>
+      <c r="F7" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="G7" s="32">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="C8" s="32">
+        <v>120.0</v>
+      </c>
+      <c r="D8" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="G8" s="32">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="C9" s="32">
+        <v>15.0</v>
+      </c>
+      <c r="D9" s="32">
+        <v>15.0</v>
+      </c>
+      <c r="E9" s="32">
+        <v>15.0</v>
+      </c>
+      <c r="F9" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="32">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="C10" s="32">
+        <v>60.0</v>
+      </c>
+      <c r="D10" s="32">
+        <v>60.0</v>
+      </c>
+      <c r="E10" s="32">
+        <v>60.0</v>
+      </c>
+      <c r="F10" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="32">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="32">
+        <v>120.0</v>
+      </c>
+      <c r="C11" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="32">
+        <v>120.0</v>
+      </c>
+      <c r="G11" s="32">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="32">
+        <v>60.0</v>
+      </c>
+      <c r="C12" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="D12" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="32">
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="32">
+        <v>60.0</v>
+      </c>
+      <c r="G12" s="32">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="32">
+        <v>120.0</v>
+      </c>
+      <c r="C13" s="32">
+        <v>120.0</v>
+      </c>
+      <c r="D13" s="32">
+        <v>120.0</v>
+      </c>
+      <c r="E13" s="32">
+        <v>120.0</v>
+      </c>
+      <c r="F13" s="32">
+        <v>120.0</v>
+      </c>
+      <c r="G13" s="32">
+        <v>120.0</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="34">
+        <f t="shared" ref="B14:G14" si="1">SUM(B4:B13)</f>
+        <v>300</v>
+      </c>
+      <c r="C14" s="34">
+        <f t="shared" si="1"/>
+        <v>315</v>
+      </c>
+      <c r="D14" s="34">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="E14" s="34">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="F14" s="34">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="G14" s="34">
+        <f t="shared" si="1"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="35">
+        <f>SUM(B14:G14)/60</f>
+        <v>31.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B15:G15">
+    <cfRule type="notContainsBlanks" dxfId="5" priority="1">
+      <formula>LEN(TRIM(B15))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/SOEN 341 Agile planning.xlsx
+++ b/SOEN 341 Agile planning.xlsx
@@ -1,19 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinpham/Documents/Concordia/SOEN 341/W-Team-SOEN341_Project_W26/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9F4AC4-2CD1-6847-AFB4-1087690653D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Cover Page" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Product backlog" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Time blog" sheetId="3" r:id="rId7"/>
+    <sheet name="Cover Page" sheetId="1" r:id="rId1"/>
+    <sheet name="Product backlog" sheetId="2" r:id="rId2"/>
+    <sheet name="Time Blog - Sprint 1" sheetId="3" r:id="rId3"/>
+    <sheet name="Time Blog - Sprint 2" sheetId="4" r:id="rId4"/>
+    <sheet name="Time Blog - Sprint 3" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="102">
   <si>
     <t>TEAM NAME</t>
   </si>
@@ -336,62 +360,151 @@
   <si>
     <t>Total hours</t>
   </si>
+  <si>
+    <t>Create recipe</t>
+  </si>
+  <si>
+    <t>Recipe details page</t>
+  </si>
+  <si>
+    <t>Search recipes</t>
+  </si>
+  <si>
+    <t>Filter recipes</t>
+  </si>
+  <si>
+    <t>Frontend–backend integration</t>
+  </si>
+  <si>
+    <t>Recipe Model</t>
+  </si>
+  <si>
+    <t>Edit Recipe</t>
+  </si>
+  <si>
+    <t>Delete Recipe</t>
+  </si>
+  <si>
+    <t>Recipe List Page</t>
+  </si>
+  <si>
+    <t>Acceptance tests (Sprint 1)</t>
+  </si>
+  <si>
+    <t>CI pipeline setup</t>
+  </si>
+  <si>
+    <t>Sprint planning</t>
+  </si>
+  <si>
+    <t>Sprint 2:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meal planner model </t>
+  </si>
+  <si>
+    <t>Create weekly meal plan</t>
+  </si>
+  <si>
+    <t>Meal planner grid UI</t>
+  </si>
+  <si>
+    <t>Assign recipes to meals</t>
+  </si>
+  <si>
+    <t>Edit meals</t>
+  </si>
+  <si>
+    <t>Prevent duplicate meals</t>
+  </si>
+  <si>
+    <t>Acceptance tests (Sprint 2)</t>
+  </si>
+  <si>
+    <t>Unit testing (Sprint 1 &amp; 2)</t>
+  </si>
+  <si>
+    <t>Ci pipeline updates</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mmmm d"/>
+    <numFmt numFmtId="164" formatCode="mmmm\ d"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="20.0"/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -400,7 +513,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -409,8 +522,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
-    <border/>
+  <borders count="11">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -424,8 +543,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -435,6 +556,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -443,35 +565,51 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -486,143 +624,173 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="38">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="15">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-      <border/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -641,60 +809,94 @@
       </border>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
         </patternFill>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Time blog-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Time blog-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="firstRowStripe" dxfId="13"/>
+      <tableStyleElement type="secondRowStripe" dxfId="12"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A3:G14">
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sprint 1:"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tin"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Guyass"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Khaled"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Jacob"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Deep"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Jinyu"/>
+  </tableColumns>
+  <tableStyleInfo name="Time blog-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7D52D4F-72F6-AC4E-AAAD-DABA4273461C}" name="Table14" displayName="Table14" ref="A1:F17">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{F271E220-8185-6543-87FD-582901246DFE}" name="Sprint 2:"/>
+    <tableColumn id="2" xr3:uid="{57E35214-B8B6-764F-A0E1-32CF9A2A75E5}" name="Tin" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{60434D5B-E5D6-8340-8423-391D76EAC69D}" name="Guyass" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{B69E75FE-DD9F-E743-B6CB-E3009D43297C}" name="Khaled" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{FCCEE399-4AB5-374F-BB8F-F0005A7361AA}" name="Jacob" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{DAFCD9B3-D1A6-C546-8AC9-079A5FE597B9}" name="Deep" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo name="Time blog-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:G14" displayName="Table1" name="Table1" id="1">
-  <tableColumns count="7">
-    <tableColumn name="Sprint 1:" id="1"/>
-    <tableColumn name="Tin" id="2"/>
-    <tableColumn name="Guyass" id="3"/>
-    <tableColumn name="Khaled" id="4"/>
-    <tableColumn name="Jacob" id="5"/>
-    <tableColumn name="Deep" id="6"/>
-    <tableColumn name="Jinyu" id="7"/>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2B8B8972-643C-C047-8176-84315C8975E4}" name="Table145" displayName="Table145" ref="A1:F15">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{15AA845B-3DFD-194E-BFF1-6823EE0940FE}" name="Sprint 2:"/>
+    <tableColumn id="2" xr3:uid="{A5A87621-5F31-2543-B95C-43026A3245E4}" name="Tin" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{7DDB9BBE-67FC-FD49-8936-3FCB0D393B0E}" name="Guyass" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{D7EE5F83-1DE6-D94F-93DB-BF13A47113AB}" name="Khaled" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{BB380029-E5DA-BA4B-8672-3C25F4D1DE3D}" name="Jacob" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{406AA7E0-55B6-E847-9DF7-FD31073E76E0}" name="Deep" dataDxfId="1"/>
   </tableColumns>
-  <tableStyleInfo name="Time blog-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Time blog-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -884,852 +1086,1542 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B1:D17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="46.5"/>
+    <col min="3" max="3" width="46.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
       <c r="C3" s="2"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" s="1"/>
       <c r="C5" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" s="1"/>
       <c r="C7" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
-      <c r="C8" s="6"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13">
+    <row r="13" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14">
+    <row r="14" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="C17" s="2"/>
       <c r="D17" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="59.88"/>
-    <col customWidth="1" min="3" max="3" width="47.5"/>
-    <col customWidth="1" min="4" max="4" width="19.75"/>
-    <col customWidth="1" min="8" max="8" width="18.38"/>
+    <col min="2" max="2" width="59.83203125" customWidth="1"/>
+    <col min="3" max="3" width="47.5" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="E2" s="14">
-        <v>46059.0</v>
-      </c>
-      <c r="F2" s="15" t="s">
+      <c r="D2" s="12">
+        <v>5</v>
+      </c>
+      <c r="E2" s="13">
+        <v>46059</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="E3" s="14">
-        <v>46059.0</v>
-      </c>
-      <c r="F3" s="15" t="s">
+      <c r="D3" s="12">
+        <v>3</v>
+      </c>
+      <c r="E3" s="13">
+        <v>46059</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="E4" s="14">
-        <v>46059.0</v>
-      </c>
-      <c r="F4" s="16" t="s">
+      <c r="D4" s="12">
+        <v>3</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46059</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="E5" s="14">
-        <v>46080.0</v>
-      </c>
-      <c r="F5" s="15" t="s">
+      <c r="D5" s="12">
+        <v>5</v>
+      </c>
+      <c r="E5" s="13">
+        <v>46080</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="E6" s="14">
-        <v>46080.0</v>
-      </c>
-      <c r="F6" s="16" t="s">
+      <c r="D6" s="12">
+        <v>3</v>
+      </c>
+      <c r="E6" s="13">
+        <v>46080</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="E7" s="14">
-        <v>46080.0</v>
-      </c>
-      <c r="F7" s="16" t="s">
+      <c r="D7" s="12">
+        <v>2</v>
+      </c>
+      <c r="E7" s="13">
+        <v>46080</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="E8" s="14">
-        <v>46080.0</v>
-      </c>
-      <c r="F8" s="16" t="s">
+      <c r="D8" s="12">
+        <v>5</v>
+      </c>
+      <c r="E8" s="13">
+        <v>46080</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="E9" s="14">
-        <v>46080.0</v>
-      </c>
-      <c r="F9" s="16" t="s">
+      <c r="D9" s="12">
+        <v>5</v>
+      </c>
+      <c r="E9" s="13">
+        <v>46080</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="E10" s="14">
-        <v>46108.0</v>
-      </c>
-      <c r="F10" s="16" t="s">
+      <c r="D10" s="12">
+        <v>5</v>
+      </c>
+      <c r="E10" s="13">
+        <v>46108</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="s">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="E11" s="14">
-        <v>46108.0</v>
-      </c>
-      <c r="F11" s="15" t="s">
+      <c r="D11" s="12">
+        <v>5</v>
+      </c>
+      <c r="E11" s="13">
+        <v>46108</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="E12" s="14">
-        <v>46108.0</v>
-      </c>
-      <c r="F12" s="16" t="s">
+      <c r="D12" s="12">
+        <v>3</v>
+      </c>
+      <c r="E12" s="13">
+        <v>46108</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="s">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="E13" s="14">
-        <v>46108.0</v>
-      </c>
-      <c r="F13" s="15" t="s">
+      <c r="D13" s="12">
+        <v>5</v>
+      </c>
+      <c r="E13" s="13">
+        <v>46108</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="s">
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="20">
-        <v>5.0</v>
-      </c>
-      <c r="E14" s="14">
-        <v>46108.0</v>
-      </c>
-      <c r="F14" s="21" t="s">
+      <c r="D14" s="16">
+        <v>5</v>
+      </c>
+      <c r="E14" s="13">
+        <v>46108</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="26">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="19">
         <f>SUM(D2:D14)</f>
         <v>54</v>
       </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
     </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G14">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G14" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Medium,Low,High"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F14">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F14" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"High,Medium"</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A2:G16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="38.88"/>
+    <col min="1" max="1" width="38.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="30" t="s">
+    <row r="2" spans="1:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="A2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="22" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="31" t="s">
+    <row r="4" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C4" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="32">
-        <v>60.0</v>
-      </c>
-      <c r="E4" s="32">
-        <v>60.0</v>
-      </c>
-      <c r="F4" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="G4" s="32">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="24">
+        <v>0</v>
+      </c>
+      <c r="C4" s="24">
+        <v>0</v>
+      </c>
+      <c r="D4" s="24">
+        <v>60</v>
+      </c>
+      <c r="E4" s="24">
+        <v>60</v>
+      </c>
+      <c r="F4" s="24">
+        <v>0</v>
+      </c>
+      <c r="G4" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C5" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="32">
-        <v>60.0</v>
-      </c>
-      <c r="E5" s="32">
-        <v>60.0</v>
-      </c>
-      <c r="F5" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="G5" s="32">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="B5" s="24">
+        <v>0</v>
+      </c>
+      <c r="C5" s="24">
+        <v>0</v>
+      </c>
+      <c r="D5" s="24">
+        <v>60</v>
+      </c>
+      <c r="E5" s="24">
+        <v>60</v>
+      </c>
+      <c r="F5" s="24">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C6" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="32">
-        <v>30.0</v>
-      </c>
-      <c r="E6" s="32">
-        <v>30.0</v>
-      </c>
-      <c r="F6" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="G6" s="32">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="33" t="s">
+      <c r="B6" s="24">
+        <v>0</v>
+      </c>
+      <c r="C6" s="24">
+        <v>0</v>
+      </c>
+      <c r="D6" s="24">
+        <v>30</v>
+      </c>
+      <c r="E6" s="24">
+        <v>30</v>
+      </c>
+      <c r="F6" s="24">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C7" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="32">
-        <v>15.0</v>
-      </c>
-      <c r="E7" s="32">
-        <v>15.0</v>
-      </c>
-      <c r="F7" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="G7" s="32">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="33" t="s">
+      <c r="B7" s="24">
+        <v>0</v>
+      </c>
+      <c r="C7" s="24">
+        <v>0</v>
+      </c>
+      <c r="D7" s="24">
+        <v>15</v>
+      </c>
+      <c r="E7" s="24">
+        <v>15</v>
+      </c>
+      <c r="F7" s="24">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C8" s="32">
-        <v>120.0</v>
-      </c>
-      <c r="D8" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="F8" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="32">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="33" t="s">
+      <c r="B8" s="24">
+        <v>0</v>
+      </c>
+      <c r="C8" s="24">
+        <v>120</v>
+      </c>
+      <c r="D8" s="24">
+        <v>0</v>
+      </c>
+      <c r="E8" s="24">
+        <v>0</v>
+      </c>
+      <c r="F8" s="24">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C9" s="32">
-        <v>15.0</v>
-      </c>
-      <c r="D9" s="32">
-        <v>15.0</v>
-      </c>
-      <c r="E9" s="32">
-        <v>15.0</v>
-      </c>
-      <c r="F9" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="32">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="33" t="s">
+      <c r="B9" s="24">
+        <v>0</v>
+      </c>
+      <c r="C9" s="24">
+        <v>15</v>
+      </c>
+      <c r="D9" s="24">
+        <v>15</v>
+      </c>
+      <c r="E9" s="24">
+        <v>15</v>
+      </c>
+      <c r="F9" s="24">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="C10" s="32">
-        <v>60.0</v>
-      </c>
-      <c r="D10" s="32">
-        <v>60.0</v>
-      </c>
-      <c r="E10" s="32">
-        <v>60.0</v>
-      </c>
-      <c r="F10" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="32">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="33" t="s">
+      <c r="B10" s="24">
+        <v>0</v>
+      </c>
+      <c r="C10" s="24">
+        <v>60</v>
+      </c>
+      <c r="D10" s="24">
+        <v>60</v>
+      </c>
+      <c r="E10" s="24">
+        <v>60</v>
+      </c>
+      <c r="F10" s="24">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="32">
-        <v>120.0</v>
-      </c>
-      <c r="C11" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="F11" s="32">
-        <v>120.0</v>
-      </c>
-      <c r="G11" s="32">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="33" t="s">
+      <c r="B11" s="24">
+        <v>120</v>
+      </c>
+      <c r="C11" s="24">
+        <v>0</v>
+      </c>
+      <c r="D11" s="24">
+        <v>0</v>
+      </c>
+      <c r="E11" s="24">
+        <v>0</v>
+      </c>
+      <c r="F11" s="24">
+        <v>120</v>
+      </c>
+      <c r="G11" s="24">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="32">
-        <v>60.0</v>
-      </c>
-      <c r="C12" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="D12" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="E12" s="32">
-        <v>0.0</v>
-      </c>
-      <c r="F12" s="32">
-        <v>60.0</v>
-      </c>
-      <c r="G12" s="32">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="33" t="s">
+      <c r="B12" s="24">
+        <v>60</v>
+      </c>
+      <c r="C12" s="24">
+        <v>0</v>
+      </c>
+      <c r="D12" s="24">
+        <v>0</v>
+      </c>
+      <c r="E12" s="24">
+        <v>0</v>
+      </c>
+      <c r="F12" s="24">
+        <v>60</v>
+      </c>
+      <c r="G12" s="24">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="32">
-        <v>120.0</v>
-      </c>
-      <c r="C13" s="32">
-        <v>120.0</v>
-      </c>
-      <c r="D13" s="32">
-        <v>120.0</v>
-      </c>
-      <c r="E13" s="32">
-        <v>120.0</v>
-      </c>
-      <c r="F13" s="32">
-        <v>120.0</v>
-      </c>
-      <c r="G13" s="32">
-        <v>120.0</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="33" t="s">
+      <c r="B13" s="24">
+        <v>120</v>
+      </c>
+      <c r="C13" s="24">
+        <v>120</v>
+      </c>
+      <c r="D13" s="24">
+        <v>120</v>
+      </c>
+      <c r="E13" s="24">
+        <v>120</v>
+      </c>
+      <c r="F13" s="24">
+        <v>120</v>
+      </c>
+      <c r="G13" s="24">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="34">
-        <f t="shared" ref="B14:G14" si="1">SUM(B4:B13)</f>
+      <c r="B14" s="26">
+        <f t="shared" ref="B14:G14" si="0">SUM(B4:B13)</f>
         <v>300</v>
       </c>
-      <c r="C14" s="34">
-        <f t="shared" si="1"/>
+      <c r="C14" s="26">
+        <f t="shared" si="0"/>
         <v>315</v>
       </c>
-      <c r="D14" s="34">
-        <f t="shared" si="1"/>
+      <c r="D14" s="26">
+        <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="E14" s="34">
-        <f t="shared" si="1"/>
+      <c r="E14" s="26">
+        <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="F14" s="34">
-        <f t="shared" si="1"/>
+      <c r="F14" s="26">
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="G14" s="34">
-        <f t="shared" si="1"/>
+      <c r="G14" s="26">
+        <f t="shared" si="0"/>
         <v>240</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="29" t="s">
+    <row r="16" spans="1:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="A16" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="21">
         <f>SUM(B14:G14)/60</f>
         <v>31.25</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:G15">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(B15))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD977B5-B58E-E345-8612-3761FD5AB99B}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="14" x14ac:dyDescent="0.15">
+      <c r="A2" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="33">
+        <v>90</v>
+      </c>
+      <c r="C2" s="33">
+        <v>0</v>
+      </c>
+      <c r="D2" s="33">
+        <v>0</v>
+      </c>
+      <c r="E2" s="33">
+        <v>0</v>
+      </c>
+      <c r="F2" s="33">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="14" x14ac:dyDescent="0.15">
+      <c r="A3" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="33">
+        <v>120</v>
+      </c>
+      <c r="C3" s="33">
+        <v>0</v>
+      </c>
+      <c r="D3" s="33">
+        <v>0</v>
+      </c>
+      <c r="E3" s="33">
+        <v>0</v>
+      </c>
+      <c r="F3" s="33">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14" x14ac:dyDescent="0.15">
+      <c r="A4" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="33">
+        <v>90</v>
+      </c>
+      <c r="C4" s="33">
+        <v>0</v>
+      </c>
+      <c r="D4" s="33">
+        <v>0</v>
+      </c>
+      <c r="E4" s="33">
+        <v>0</v>
+      </c>
+      <c r="F4" s="33">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="33">
+        <v>60</v>
+      </c>
+      <c r="C5" s="33">
+        <v>0</v>
+      </c>
+      <c r="D5" s="33">
+        <v>0</v>
+      </c>
+      <c r="E5" s="33">
+        <v>0</v>
+      </c>
+      <c r="F5" s="33">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33">
+        <v>30</v>
+      </c>
+      <c r="D6" s="33">
+        <v>120</v>
+      </c>
+      <c r="E6" s="33">
+        <v>120</v>
+      </c>
+      <c r="F6" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="33">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33">
+        <v>0</v>
+      </c>
+      <c r="D7" s="33">
+        <v>90</v>
+      </c>
+      <c r="E7" s="33">
+        <v>90</v>
+      </c>
+      <c r="F7" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33">
+        <v>0</v>
+      </c>
+      <c r="D8" s="33">
+        <v>60</v>
+      </c>
+      <c r="E8" s="33">
+        <v>60</v>
+      </c>
+      <c r="F8" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="33">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33">
+        <v>0</v>
+      </c>
+      <c r="D9" s="33">
+        <v>0</v>
+      </c>
+      <c r="E9" s="33">
+        <v>0</v>
+      </c>
+      <c r="F9" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33">
+        <v>120</v>
+      </c>
+      <c r="D10" s="33">
+        <v>0</v>
+      </c>
+      <c r="E10" s="33">
+        <v>30</v>
+      </c>
+      <c r="F10" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A11" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="33">
+        <v>0</v>
+      </c>
+      <c r="C11" s="33">
+        <v>150</v>
+      </c>
+      <c r="D11" s="33">
+        <v>30</v>
+      </c>
+      <c r="E11" s="33">
+        <v>30</v>
+      </c>
+      <c r="F11" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="34">
+        <v>30</v>
+      </c>
+      <c r="C12" s="34">
+        <v>0</v>
+      </c>
+      <c r="D12" s="34">
+        <v>0</v>
+      </c>
+      <c r="E12" s="34">
+        <v>0</v>
+      </c>
+      <c r="F12" s="34">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A13" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="34">
+        <v>120</v>
+      </c>
+      <c r="C13" s="34">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
+        <v>0</v>
+      </c>
+      <c r="E13" s="34">
+        <v>0</v>
+      </c>
+      <c r="F13" s="34">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A14" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="34">
+        <v>30</v>
+      </c>
+      <c r="C14" s="34">
+        <v>30</v>
+      </c>
+      <c r="D14" s="34">
+        <v>30</v>
+      </c>
+      <c r="E14" s="34">
+        <v>30</v>
+      </c>
+      <c r="F14" s="34">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A15" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="34">
+        <v>30</v>
+      </c>
+      <c r="C15" s="34">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
+        <v>0</v>
+      </c>
+      <c r="E15" s="34">
+        <v>0</v>
+      </c>
+      <c r="F15" s="34">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A16" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="34">
+        <v>120</v>
+      </c>
+      <c r="C16" s="34">
+        <v>120</v>
+      </c>
+      <c r="D16" s="34">
+        <v>120</v>
+      </c>
+      <c r="E16" s="34">
+        <v>120</v>
+      </c>
+      <c r="F16" s="34">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A17" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="35">
+        <f>SUM(B2:B16)</f>
+        <v>690</v>
+      </c>
+      <c r="C17" s="35">
+        <f t="shared" ref="C17:F17" si="0">SUM(C2:C16)</f>
+        <v>450</v>
+      </c>
+      <c r="D17" s="35">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="E17" s="35">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="F17" s="35">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E91D483F-8C80-4541-A49B-B3B34875CD37}">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="37"/>
+    </row>
+    <row r="2" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="33">
+        <v>90</v>
+      </c>
+      <c r="C2" s="33">
+        <v>0</v>
+      </c>
+      <c r="D2" s="33">
+        <v>0</v>
+      </c>
+      <c r="E2" s="33">
+        <v>0</v>
+      </c>
+      <c r="F2" s="33">
+        <v>90</v>
+      </c>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="A3" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="33">
+        <v>0</v>
+      </c>
+      <c r="C3" s="33">
+        <v>0</v>
+      </c>
+      <c r="D3" s="33">
+        <v>0</v>
+      </c>
+      <c r="E3" s="33">
+        <v>0</v>
+      </c>
+      <c r="F3" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="A4" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="33">
+        <v>0</v>
+      </c>
+      <c r="C4" s="33">
+        <v>0</v>
+      </c>
+      <c r="D4" s="33">
+        <v>120</v>
+      </c>
+      <c r="E4" s="33">
+        <v>60</v>
+      </c>
+      <c r="F4" s="33">
+        <v>0</v>
+      </c>
+      <c r="H4" s="27"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A5" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="33">
+        <v>0</v>
+      </c>
+      <c r="C5" s="33">
+        <v>0</v>
+      </c>
+      <c r="D5" s="33">
+        <v>60</v>
+      </c>
+      <c r="E5" s="33">
+        <v>60</v>
+      </c>
+      <c r="F5" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A6" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33">
+        <v>30</v>
+      </c>
+      <c r="D6" s="33">
+        <v>0</v>
+      </c>
+      <c r="E6" s="33">
+        <v>0</v>
+      </c>
+      <c r="F6" s="33">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A7" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="33">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33">
+        <v>0</v>
+      </c>
+      <c r="D7" s="33">
+        <v>0</v>
+      </c>
+      <c r="E7" s="33">
+        <v>60</v>
+      </c>
+      <c r="F7" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A8" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="33">
+        <v>60</v>
+      </c>
+      <c r="C8" s="33">
+        <v>0</v>
+      </c>
+      <c r="D8" s="33">
+        <v>60</v>
+      </c>
+      <c r="E8" s="33">
+        <v>0</v>
+      </c>
+      <c r="F8" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A9" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="33">
+        <v>30</v>
+      </c>
+      <c r="C9" s="33">
+        <v>0</v>
+      </c>
+      <c r="D9" s="33">
+        <v>0</v>
+      </c>
+      <c r="E9" s="33">
+        <v>0</v>
+      </c>
+      <c r="F9" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A10" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33">
+        <v>120</v>
+      </c>
+      <c r="D10" s="33">
+        <v>0</v>
+      </c>
+      <c r="E10" s="33">
+        <v>30</v>
+      </c>
+      <c r="F10" s="33">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A11" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="33">
+        <v>60</v>
+      </c>
+      <c r="C11" s="33">
+        <v>60</v>
+      </c>
+      <c r="D11" s="33">
+        <v>0</v>
+      </c>
+      <c r="E11" s="33">
+        <v>0</v>
+      </c>
+      <c r="F11" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A12" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="34">
+        <v>30</v>
+      </c>
+      <c r="C12" s="34">
+        <v>30</v>
+      </c>
+      <c r="D12" s="34">
+        <v>30</v>
+      </c>
+      <c r="E12" s="34">
+        <v>30</v>
+      </c>
+      <c r="F12" s="34">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A13" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="34">
+        <v>30</v>
+      </c>
+      <c r="C13" s="34">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
+        <v>0</v>
+      </c>
+      <c r="E13" s="34">
+        <v>0</v>
+      </c>
+      <c r="F13" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A14" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="34">
+        <v>60</v>
+      </c>
+      <c r="C14" s="34">
+        <v>60</v>
+      </c>
+      <c r="D14" s="34">
+        <v>60</v>
+      </c>
+      <c r="E14" s="34">
+        <v>60</v>
+      </c>
+      <c r="F14" s="34">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A15" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="35">
+        <f>SUM(B2:B14)</f>
+        <v>360</v>
+      </c>
+      <c r="C15" s="35">
+        <f>SUM(C2:C14)</f>
+        <v>300</v>
+      </c>
+      <c r="D15" s="35">
+        <f>SUM(D2:D14)</f>
+        <v>330</v>
+      </c>
+      <c r="E15" s="35">
+        <f>SUM(E2:E14)</f>
+        <v>300</v>
+      </c>
+      <c r="F15" s="35">
+        <f>SUM(F2:F14)</f>
+        <v>360</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>